--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486824_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486824_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5381</v>
+        <v>3.7794</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2083</v>
+        <v>5.8288</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6702</v>
+        <v>-2.0494</v>
       </c>
       <c r="G2" t="n">
         <v>7.5859</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.7441</v>
+        <v>-3.5027</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4347</v>
+        <v>-0.8142</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.3093</v>
+        <v>-2.6885</v>
       </c>
       <c r="V2" t="n">
         <v>1.0478</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6674</v>
+        <v>-0.2248</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6713</v>
+        <v>2.1884</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3387</v>
+        <v>-2.4132</v>
       </c>
       <c r="G3" t="n">
         <v>6.5735</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2763</v>
+        <v>-2.8337</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1588</v>
+        <v>-0.6417</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.1175</v>
+        <v>-2.192</v>
       </c>
       <c r="V3" t="n">
         <v>-2.2269</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.9113</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5039</v>
+        <v>-1.195</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2252</v>
+        <v>0.2838</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7648</v>
+        <v>-1.0918</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0339</v>
+        <v>-0.1175</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.269</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6074</v>
+        <v>-1.2362</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4831</v>
+        <v>0.0207</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1244</v>
+        <v>-1.2569</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1574</v>
+        <v>0.1443</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5508</v>
+        <v>-0.1382</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3934</v>
+        <v>0.2826</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4024</v>
+        <v>-0.0828</v>
       </c>
       <c r="T4" t="n">
-        <v>0.248</v>
+        <v>0.0412</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6504</v>
+        <v>-0.124</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.0837</v>
+        <v>-0.1228</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.6976</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8782</v>
+        <v>-0.9737</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9882</v>
+        <v>2.4005</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1099</v>
+        <v>-3.3742</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0918</v>
+        <v>2.7648</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1175</v>
+        <v>3.0339</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.269</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2362</v>
+        <v>2.6074</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>2.4831</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2569</v>
+        <v>0.1244</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1443</v>
+        <v>0.1574</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1382</v>
+        <v>0.5508</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2826</v>
+        <v>-0.3934</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0498</v>
+        <v>-0.6548</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>0.1446</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2978</v>
+        <v>-0.7994</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1228</v>
+        <v>-3.0837</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1228</v>
+        <v>-3.6976</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1953</v>
+        <v>-1.58</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2558</v>
+        <v>-1.5661</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0605</v>
+        <v>-0.014</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0628</v>
@@ -922,13 +922,13 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4467</v>
+        <v>0.062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3584</v>
+        <v>0.0481</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>L. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5865</v>
+        <v>-2.817</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9913</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5952</v>
+        <v>-3.6713</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0104</v>
+        <v>-1.6707</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3518</v>
+        <v>-1.3453</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3415</v>
+        <v>-0.3254</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1922</v>
+        <v>0.4404</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2156</v>
+        <v>0.1035</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9766</v>
+        <v>0.337</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1819</v>
+        <v>-2.1112</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1362</v>
+        <v>-1.4488</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3181</v>
+        <v>-0.6624</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2823</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.7923</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1936</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3232</v>
+        <v>-0.4623</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1296</v>
+        <v>-0.4686</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5081</v>
+        <v>-0.4084</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>1.8415</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7937</v>
+        <v>-2.2499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA SANCHEZ</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9286</v>
+        <v>-3.2885</v>
       </c>
       <c r="E8" t="n">
-        <v>0.544</v>
+        <v>-1.7855</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4726</v>
+        <v>-1.503</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6707</v>
+        <v>-1.9548</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3453</v>
+        <v>-0.3317</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3254</v>
+        <v>-1.6231</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4404</v>
+        <v>-1.2916</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1035</v>
+        <v>-0.6067</v>
       </c>
       <c r="L8" t="n">
-        <v>0.337</v>
+        <v>-0.6849</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1112</v>
+        <v>-0.6632</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4488</v>
+        <v>0.275</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6624</v>
+        <v>-0.9382</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0425</v>
+        <v>-1.6204</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7725</v>
+        <v>-0.7795</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.27</v>
+        <v>-0.8409</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4084</v>
+        <v>-1.0648</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8415</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2499</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7148</v>
+        <v>-3.6967</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8889</v>
+        <v>-2.2324</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8259</v>
+        <v>-1.4643</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9548</v>
+        <v>2.0104</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3317</v>
+        <v>2.3518</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6231</v>
+        <v>-0.3415</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2916</v>
+        <v>3.1922</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6067</v>
+        <v>2.2156</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6849</v>
+        <v>0.9766</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6632</v>
+        <v>-1.1819</v>
       </c>
       <c r="N9" t="n">
-        <v>0.275</v>
+        <v>0.1362</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9382</v>
+        <v>-1.3181</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3515</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-5.7923</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>2.51</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0467</v>
+        <v>-1.9166</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8829</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1637</v>
+        <v>-1.9987</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0648</v>
+        <v>-0.5081</v>
       </c>
       <c r="W9" t="n">
         <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3505</v>
+        <v>-0.7937</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7632</v>
+        <v>-3.8458</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2465</v>
+        <v>-1.4534</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5166</v>
+        <v>-2.3925</v>
       </c>
       <c r="G10" t="n">
         <v>-2.981</v>
@@ -1234,13 +1234,13 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0758</v>
+        <v>-1.1585</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0825</v>
+        <v>-0.1244</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1583</v>
+        <v>-1.0341</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8569</v>
+        <v>-4.2156</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6439</v>
+        <v>-1.1268</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2129</v>
+        <v>-3.0888</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2456</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6201</v>
+        <v>-1.9788</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7725</v>
+        <v>-0.2554</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8475</v>
+        <v>-1.7234</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5704</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.7741</v>
+        <v>-17.774</v>
       </c>
       <c r="E12" t="n">
-        <v>1.912899999999998</v>
+        <v>1.912800000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-19.6869</v>
@@ -1360,7 +1360,7 @@
         <v>11.7196</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7916</v>
+        <v>-2.791599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>17.5967</v>
@@ -1390,10 +1390,10 @@
         <v>13.5155</v>
       </c>
       <c r="S12" t="n">
-        <v>-14.6174</v>
+        <v>-14.6172</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7613</v>
+        <v>-2.7615</v>
       </c>
       <c r="U12" t="n">
         <v>-11.8557</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1228</v>
+        <v>10.2274</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7685</v>
+        <v>8.699299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3544</v>
+        <v>1.5282</v>
       </c>
       <c r="G13" t="n">
         <v>7.5987</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2538</v>
+        <v>1.3584</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0004</v>
+        <v>0.9304</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2541</v>
+        <v>0.428</v>
       </c>
       <c r="V13" t="n">
         <v>1.2703</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7301</v>
+        <v>4.9921</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6336</v>
+        <v>4.0131</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0965</v>
+        <v>0.979</v>
       </c>
       <c r="G14" t="n">
         <v>-3.0834</v>
@@ -1546,13 +1546,13 @@
         <v>3.0892</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3235</v>
+        <v>3.5856</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0331</v>
+        <v>2.4126</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2904</v>
+        <v>1.173</v>
       </c>
       <c r="V14" t="n">
         <v>4.2969</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9862</v>
+        <v>2.6665</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7366</v>
+        <v>4.4914</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2496</v>
+        <v>-1.825</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.321</v>
+        <v>-1.2605</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.0195</v>
+        <v>-3.4692</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6984</v>
+        <v>2.2087</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1563</v>
+        <v>1.8787</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0878</v>
+        <v>-0.572</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2442</v>
+        <v>2.4507</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4774</v>
+        <v>-3.1392</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9316</v>
+        <v>-2.8972</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4543</v>
+        <v>-0.242</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>7.5349</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>6.8393</v>
+        <v>0.6408</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6957</v>
+        <v>0.3175</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6138</v>
+        <v>3.3548</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3282</v>
+        <v>4.8681</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2617</v>
+        <v>1.8575</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7908</v>
+        <v>0.8065</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5292</v>
+        <v>1.051</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8536</v>
+        <v>-1.321</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.9304</v>
+        <v>-2.0195</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.6984</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9560999999999999</v>
+        <v>0.1563</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6886</v>
+        <v>-0.0878</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7325</v>
+        <v>0.2442</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8975</v>
+        <v>-1.4774</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2418</v>
+        <v>-1.9316</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.4543</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2504</v>
+        <v>3.4062</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2336</v>
+        <v>2.9092</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0168</v>
+        <v>0.497</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5133</v>
+        <v>-0.6138</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5133</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.842</v>
+        <v>1.2523</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9401</v>
+        <v>1.7566</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0981</v>
+        <v>-0.5043</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2605</v>
+        <v>-2.8536</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.4692</v>
+        <v>-2.9304</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2087</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8787</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.572</v>
+        <v>-1.6886</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4507</v>
+        <v>0.7325</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1392</v>
+        <v>-1.8975</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.8972</v>
+        <v>-1.2418</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.242</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.51</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8662</v>
+        <v>1.241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9106</v>
+        <v>1.1994</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0443</v>
+        <v>0.0416</v>
       </c>
       <c r="V17" t="n">
-        <v>3.3548</v>
+        <v>1.5133</v>
       </c>
       <c r="W17" t="n">
-        <v>4.8681</v>
+        <v>1.5133</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5082</v>
+        <v>0.6613</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0062</v>
+        <v>0.1096</v>
       </c>
       <c r="F18" t="n">
-        <v>0.502</v>
+        <v>0.5516</v>
       </c>
       <c r="G18" t="n">
         <v>0.3372</v>
@@ -1858,13 +1858,13 @@
         <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0221</v>
+        <v>0.131</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2771</v>
+        <v>0.5585</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0207</v>
+        <v>0.2275</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2564</v>
+        <v>0.3309</v>
       </c>
       <c r="G19" t="n">
         <v>0.2275</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0497</v>
+        <v>0.331</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2068</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1451</v>
+        <v>-0.9288</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4294</v>
+        <v>0.5484</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7157</v>
+        <v>-1.4772</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1713</v>
+        <v>-2.3063</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3303</v>
+        <v>-1.2619</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.841</v>
+        <v>-1.0444</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1771</v>
+        <v>-0.2016</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4287</v>
+        <v>0.6009</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6058</v>
+        <v>-0.8024</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9942</v>
+        <v>-2.1047</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.759</v>
+        <v>-1.8628</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2352</v>
+        <v>-0.242</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2594</v>
+        <v>1.2962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1652</v>
+        <v>1.1441</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4246</v>
+        <v>0.1521</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3282</v>
+        <v>-1.2703</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5133</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
         <v>-1.8415</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7159</v>
+        <v>-1.2307</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3132</v>
+        <v>0.0877</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4027</v>
+        <v>-1.3184</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3063</v>
+        <v>-1.1713</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2619</v>
+        <v>-0.3303</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0444</v>
+        <v>-0.841</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2016</v>
+        <v>-0.1771</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6009</v>
+        <v>0.4287</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8024</v>
+        <v>-0.6058</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1047</v>
+        <v>-0.9942</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8628</v>
+        <v>-0.759</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.242</v>
+        <v>-0.2352</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3515</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4909</v>
+        <v>0.655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7175</v>
+        <v>0.6823</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2266</v>
+        <v>-0.0273</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2703</v>
+        <v>-0.3282</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5712</v>
+        <v>1.5133</v>
       </c>
       <c r="X21" t="n">
         <v>-1.8415</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.093</v>
+        <v>-2.282</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4669</v>
+        <v>-1.0532</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6261</v>
+        <v>-1.2288</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0951</v>
@@ -2170,13 +2170,13 @@
         <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8436</v>
+        <v>1.6546</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2682</v>
+        <v>1.6819</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4246</v>
+        <v>-0.0273</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>17.7741</v>
       </c>
       <c r="E23" t="n">
-        <v>19.687</v>
+        <v>19.6869</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.912900000000001</v>
+        <v>-1.913</v>
       </c>
       <c r="G23" t="n">
         <v>-8.927800000000001</v>
@@ -2218,7 +2218,7 @@
         <v>-11.7196</v>
       </c>
       <c r="I23" t="n">
-        <v>2.791699999999999</v>
+        <v>2.7917</v>
       </c>
       <c r="J23" t="n">
         <v>8.668900000000001</v>
@@ -2227,7 +2227,7 @@
         <v>2.7681</v>
       </c>
       <c r="L23" t="n">
-        <v>5.9009</v>
+        <v>5.900899999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-17.5968</v>
@@ -2239,7 +2239,7 @@
         <v>-3.1092</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8615</v>
+        <v>3.861499999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5156</v>
@@ -2248,13 +2248,13 @@
         <v>17.3769</v>
       </c>
       <c r="S23" t="n">
-        <v>14.6173</v>
+        <v>14.6172</v>
       </c>
       <c r="T23" t="n">
         <v>11.8557</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7615</v>
+        <v>2.7616</v>
       </c>
       <c r="V23" t="n">
         <v>8.222999999999999</v>
